--- a/ROSA_vitaSPEC/Results/xgboost/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
+++ b/ROSA_vitaSPEC/Results/xgboost/moyennes/Results/meso_frais/total.trans.carotene.natif/RANDOMSEARCH_DETAILS_total.trans.carotene.natif.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,13 +481,13 @@
         <v>0.9997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7111</v>
+        <v>0.7127</v>
       </c>
       <c r="G2" t="n">
-        <v>21.0627</v>
+        <v>21.0711</v>
       </c>
       <c r="H2" t="n">
-        <v>348.0699</v>
+        <v>347.111</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6539</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8765</v>
+        <v>8.861000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>380.9512</v>
+        <v>381.6328</v>
       </c>
     </row>
     <row r="4">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9804</v>
+        <v>0.9806</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.0455</v>
+        <v>-0.0368</v>
       </c>
       <c r="G55" t="n">
-        <v>353.6289</v>
+        <v>353.0156</v>
       </c>
       <c r="H55" t="n">
-        <v>662.1512</v>
+        <v>659.3986</v>
       </c>
     </row>
     <row r="56">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9851</v>
+        <v>0.985</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.0324</v>
+        <v>-0.0349</v>
       </c>
       <c r="G56" t="n">
-        <v>351.3571</v>
+        <v>352.1883</v>
       </c>
       <c r="H56" t="n">
-        <v>657.9946</v>
+        <v>658.7965</v>
       </c>
     </row>
     <row r="57">
@@ -2609,29 +2609,29 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0.9811</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6757</v>
+        <v>-0.0203</v>
       </c>
       <c r="G69" t="n">
-        <v>4.1584</v>
+        <v>358.8237</v>
       </c>
       <c r="H69" t="n">
-        <v>368.7965</v>
+        <v>654.1254</v>
       </c>
     </row>
     <row r="70">
@@ -2641,29 +2641,29 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9958</v>
+        <v>0.9802</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7541</v>
+        <v>0.0071</v>
       </c>
       <c r="G70" t="n">
-        <v>67.6617</v>
+        <v>359.9244</v>
       </c>
       <c r="H70" t="n">
-        <v>321.1263</v>
+        <v>645.289</v>
       </c>
     </row>
     <row r="71">
@@ -2673,29 +2673,29 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9966</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6889999999999999</v>
+        <v>-0.0199</v>
       </c>
       <c r="G71" t="n">
-        <v>62.9225</v>
+        <v>0.0028</v>
       </c>
       <c r="H71" t="n">
-        <v>361.1414</v>
+        <v>654.0069</v>
       </c>
     </row>
     <row r="72">
@@ -2705,29 +2705,29 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7089</v>
+        <v>-0.0023</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0238</v>
+        <v>348.9712</v>
       </c>
       <c r="H72" t="n">
-        <v>349.3685</v>
+        <v>648.3411</v>
       </c>
     </row>
     <row r="73">
@@ -2737,29 +2737,29 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6365</v>
+        <v>0.6757</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4038</v>
+        <v>4.1584</v>
       </c>
       <c r="H73" t="n">
-        <v>390.4514</v>
+        <v>368.7965</v>
       </c>
     </row>
     <row r="74">
@@ -2769,29 +2769,29 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9998</v>
+        <v>0.9958</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7541</v>
       </c>
       <c r="G74" t="n">
-        <v>14.1991</v>
+        <v>67.6617</v>
       </c>
       <c r="H74" t="n">
-        <v>354.0642</v>
+        <v>321.1263</v>
       </c>
     </row>
     <row r="75">
@@ -2801,29 +2801,29 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9912</v>
+        <v>0.9966</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5454</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>120.1305</v>
+        <v>62.9225</v>
       </c>
       <c r="H75" t="n">
-        <v>436.6193</v>
+        <v>361.1414</v>
       </c>
     </row>
     <row r="76">
@@ -2833,29 +2833,29 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9912</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5454</v>
+        <v>0.7089</v>
       </c>
       <c r="G76" t="n">
-        <v>120.1305</v>
+        <v>0.0238</v>
       </c>
       <c r="H76" t="n">
-        <v>436.6193</v>
+        <v>349.3685</v>
       </c>
     </row>
     <row r="77">
@@ -2865,29 +2865,29 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9752</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.025</v>
+        <v>0.6365</v>
       </c>
       <c r="G77" t="n">
-        <v>370.7691</v>
+        <v>0.4038</v>
       </c>
       <c r="H77" t="n">
-        <v>639.4481</v>
+        <v>390.4514</v>
       </c>
     </row>
     <row r="78">
@@ -2897,29 +2897,29 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.9739</v>
+        <v>0.9998</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0209</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>373.3617</v>
+        <v>14.1991</v>
       </c>
       <c r="H78" t="n">
-        <v>640.7683</v>
+        <v>354.0642</v>
       </c>
     </row>
     <row r="79">
@@ -2929,29 +2929,29 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9735</v>
+        <v>0.9912</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0222</v>
+        <v>0.5454</v>
       </c>
       <c r="G79" t="n">
-        <v>373.9972</v>
+        <v>120.1305</v>
       </c>
       <c r="H79" t="n">
-        <v>640.3667</v>
+        <v>436.6193</v>
       </c>
     </row>
     <row r="80">
@@ -2961,29 +2961,29 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9744</v>
+        <v>0.9912</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0172</v>
+        <v>0.5454</v>
       </c>
       <c r="G80" t="n">
-        <v>372.9642</v>
+        <v>120.1305</v>
       </c>
       <c r="H80" t="n">
-        <v>641.994</v>
+        <v>436.6193</v>
       </c>
     </row>
     <row r="81">
@@ -2993,11 +2993,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.9829</v>
+        <v>0.9752</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.0136</v>
+        <v>0.025</v>
       </c>
       <c r="G81" t="n">
-        <v>353.2224</v>
+        <v>370.7691</v>
       </c>
       <c r="H81" t="n">
-        <v>651.9766</v>
+        <v>639.4481</v>
       </c>
     </row>
     <row r="82">
@@ -3025,11 +3025,11 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.979</v>
+        <v>0.9739</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.0229</v>
+        <v>0.0209</v>
       </c>
       <c r="G82" t="n">
-        <v>355.875</v>
+        <v>373.3617</v>
       </c>
       <c r="H82" t="n">
-        <v>654.9686</v>
+        <v>640.7683</v>
       </c>
     </row>
     <row r="83">
@@ -3057,29 +3057,29 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9913</v>
+        <v>0.9735</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5452</v>
+        <v>0.0222</v>
       </c>
       <c r="G83" t="n">
-        <v>119.9258</v>
+        <v>373.9972</v>
       </c>
       <c r="H83" t="n">
-        <v>436.7444</v>
+        <v>640.3667</v>
       </c>
     </row>
     <row r="84">
@@ -3089,29 +3089,29 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.991</v>
+        <v>0.9744</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.0172</v>
       </c>
       <c r="G84" t="n">
-        <v>96.1639</v>
+        <v>372.9642</v>
       </c>
       <c r="H84" t="n">
-        <v>437.3509</v>
+        <v>641.994</v>
       </c>
     </row>
     <row r="85">
@@ -3121,29 +3121,29 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9913</v>
+        <v>0.9829</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5459000000000001</v>
+        <v>-0.0136</v>
       </c>
       <c r="G85" t="n">
-        <v>94.9118</v>
+        <v>353.2224</v>
       </c>
       <c r="H85" t="n">
-        <v>436.4111</v>
+        <v>651.9766</v>
       </c>
     </row>
     <row r="86">
@@ -3153,29 +3153,29 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0.979</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.0229</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0004</v>
+        <v>355.875</v>
       </c>
       <c r="H86" t="n">
-        <v>358.1512</v>
+        <v>654.9686</v>
       </c>
     </row>
     <row r="87">
@@ -3185,29 +3185,29 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0.9913</v>
       </c>
       <c r="F87" t="n">
-        <v>0.711</v>
+        <v>0.5452</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005</v>
+        <v>119.9258</v>
       </c>
       <c r="H87" t="n">
-        <v>348.1277</v>
+        <v>436.7444</v>
       </c>
     </row>
     <row r="88">
@@ -3217,29 +3217,29 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.991</v>
       </c>
       <c r="F88" t="n">
-        <v>0.6963</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0005</v>
+        <v>96.1639</v>
       </c>
       <c r="H88" t="n">
-        <v>356.8669</v>
+        <v>437.3509</v>
       </c>
     </row>
     <row r="89">
@@ -3249,11 +3249,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9959</v>
+        <v>0.9913</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6872</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>68.1144</v>
+        <v>94.9118</v>
       </c>
       <c r="H89" t="n">
-        <v>362.2001</v>
+        <v>436.4111</v>
       </c>
     </row>
     <row r="90">
@@ -3281,29 +3281,29 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>0.6604</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>12.305</v>
+        <v>0.0004</v>
       </c>
       <c r="H90" t="n">
-        <v>377.3658</v>
+        <v>358.1512</v>
       </c>
     </row>
     <row r="91">
@@ -3313,29 +3313,29 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6987</v>
+        <v>0.711</v>
       </c>
       <c r="G91" t="n">
-        <v>13.5249</v>
+        <v>0.0005</v>
       </c>
       <c r="H91" t="n">
-        <v>355.4855</v>
+        <v>348.1277</v>
       </c>
     </row>
     <row r="92">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3377,29 +3377,29 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9998</v>
+        <v>0.9959</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6987</v>
+        <v>0.6872</v>
       </c>
       <c r="G93" t="n">
-        <v>13.5249</v>
+        <v>68.1144</v>
       </c>
       <c r="H93" t="n">
-        <v>355.4855</v>
+        <v>362.2001</v>
       </c>
     </row>
     <row r="94">
@@ -3409,29 +3409,29 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5797</v>
+        <v>0.6604</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0027</v>
+        <v>12.305</v>
       </c>
       <c r="H94" t="n">
-        <v>419.8115</v>
+        <v>377.3658</v>
       </c>
     </row>
     <row r="95">
@@ -3441,29 +3441,29 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8908</v>
+        <v>0.9998</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.032</v>
+        <v>0.6987</v>
       </c>
       <c r="G95" t="n">
-        <v>452.2002</v>
+        <v>13.5249</v>
       </c>
       <c r="H95" t="n">
-        <v>657.8627</v>
+        <v>355.4855</v>
       </c>
     </row>
     <row r="96">
@@ -3473,29 +3473,29 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9865</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0.5628</v>
+        <v>0.6963</v>
       </c>
       <c r="G96" t="n">
-        <v>120.1966</v>
+        <v>0.0005</v>
       </c>
       <c r="H96" t="n">
-        <v>428.2051</v>
+        <v>356.8669</v>
       </c>
     </row>
     <row r="97">
@@ -3505,29 +3505,29 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5718</v>
+        <v>0.6987</v>
       </c>
       <c r="G97" t="n">
-        <v>0.3328</v>
+        <v>13.5249</v>
       </c>
       <c r="H97" t="n">
-        <v>423.7642</v>
+        <v>355.4855</v>
       </c>
     </row>
     <row r="98">
@@ -3537,29 +3537,29 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0.6851</v>
+        <v>0.5797</v>
       </c>
       <c r="G98" t="n">
-        <v>13.6572</v>
+        <v>0.0027</v>
       </c>
       <c r="H98" t="n">
-        <v>363.3902</v>
+        <v>419.8115</v>
       </c>
     </row>
     <row r="99">
@@ -3569,29 +3569,29 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0.8908</v>
       </c>
       <c r="F99" t="n">
-        <v>0.7015</v>
+        <v>-0.032</v>
       </c>
       <c r="G99" t="n">
-        <v>0.012</v>
+        <v>452.2002</v>
       </c>
       <c r="H99" t="n">
-        <v>353.8072</v>
+        <v>657.8627</v>
       </c>
     </row>
     <row r="100">
@@ -3601,29 +3601,29 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6659</v>
+        <v>0.5628</v>
       </c>
       <c r="G100" t="n">
-        <v>4.7042</v>
+        <v>120.1966</v>
       </c>
       <c r="H100" t="n">
-        <v>374.3147</v>
+        <v>428.2051</v>
       </c>
     </row>
     <row r="101">
@@ -3633,29 +3633,29 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>0.6737</v>
+        <v>0.5718</v>
       </c>
       <c r="G101" t="n">
-        <v>24.7796</v>
+        <v>0.3328</v>
       </c>
       <c r="H101" t="n">
-        <v>369.9047</v>
+        <v>423.7642</v>
       </c>
     </row>
     <row r="102">
@@ -3665,29 +3665,29 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9927</v>
+        <v>0.9998</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6851</v>
       </c>
       <c r="G102" t="n">
-        <v>86.3524</v>
+        <v>13.6572</v>
       </c>
       <c r="H102" t="n">
-        <v>386.0071</v>
+        <v>363.3902</v>
       </c>
     </row>
     <row r="103">
@@ -3697,29 +3697,29 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E103" t="n">
         <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6933</v>
+        <v>0.7015</v>
       </c>
       <c r="G103" t="n">
-        <v>1.6381</v>
+        <v>0.012</v>
       </c>
       <c r="H103" t="n">
-        <v>358.6471</v>
+        <v>353.8072</v>
       </c>
     </row>
     <row r="104">
@@ -3729,29 +3729,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.6659</v>
       </c>
       <c r="G104" t="n">
-        <v>13.7581</v>
+        <v>4.7042</v>
       </c>
       <c r="H104" t="n">
-        <v>349.2204</v>
+        <v>374.3147</v>
       </c>
     </row>
     <row r="105">
@@ -3761,29 +3761,29 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7063</v>
+        <v>0.6737</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0036</v>
+        <v>24.7796</v>
       </c>
       <c r="H105" t="n">
-        <v>350.9487</v>
+        <v>369.9047</v>
       </c>
     </row>
     <row r="106">
@@ -3793,29 +3793,29 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0.9927</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6927</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0003</v>
+        <v>86.3524</v>
       </c>
       <c r="H106" t="n">
-        <v>358.9785</v>
+        <v>386.0071</v>
       </c>
     </row>
     <row r="107">
@@ -3825,29 +3825,29 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>1</v>
       </c>
       <c r="F107" t="n">
-        <v>0.6673</v>
+        <v>0.6933</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0004</v>
+        <v>1.6381</v>
       </c>
       <c r="H107" t="n">
-        <v>373.5235</v>
+        <v>358.6471</v>
       </c>
     </row>
     <row r="108">
@@ -3857,29 +3857,29 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F108" t="n">
-        <v>0.6506</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0003</v>
+        <v>13.7581</v>
       </c>
       <c r="H108" t="n">
-        <v>382.7965</v>
+        <v>349.2204</v>
       </c>
     </row>
     <row r="109">
@@ -3889,29 +3889,29 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F109" t="n">
-        <v>0.654</v>
+        <v>0.7063</v>
       </c>
       <c r="G109" t="n">
-        <v>11.3676</v>
+        <v>0.0036</v>
       </c>
       <c r="H109" t="n">
-        <v>380.9043</v>
+        <v>350.9487</v>
       </c>
     </row>
     <row r="110">
@@ -3921,29 +3921,29 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7258</v>
+        <v>0.6927</v>
       </c>
       <c r="G110" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.0003</v>
       </c>
       <c r="H110" t="n">
-        <v>339.0828</v>
+        <v>358.9785</v>
       </c>
     </row>
     <row r="111">
@@ -3953,29 +3953,29 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.7048</v>
+        <v>0.6673</v>
       </c>
       <c r="G111" t="n">
-        <v>15.2739</v>
+        <v>0.0004</v>
       </c>
       <c r="H111" t="n">
-        <v>351.8625</v>
+        <v>373.5235</v>
       </c>
     </row>
     <row r="112">
@@ -3985,29 +3985,29 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6365</v>
+        <v>0.6506</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2858</v>
+        <v>0.0003</v>
       </c>
       <c r="H112" t="n">
-        <v>390.426</v>
+        <v>382.7965</v>
       </c>
     </row>
     <row r="113">
@@ -4017,11 +4017,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4033,13 +4033,13 @@
         <v>0.9999</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6472</v>
+        <v>0.654</v>
       </c>
       <c r="G113" t="n">
-        <v>11.6211</v>
+        <v>11.3676</v>
       </c>
       <c r="H113" t="n">
-        <v>384.6211</v>
+        <v>380.9043</v>
       </c>
     </row>
     <row r="114">
@@ -4049,11 +4049,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4065,13 +4065,13 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7207</v>
+        <v>0.7258</v>
       </c>
       <c r="G114" t="n">
-        <v>0.458</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>342.2374</v>
+        <v>339.0828</v>
       </c>
     </row>
     <row r="115">
@@ -4081,29 +4081,29 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7048</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0005</v>
+        <v>15.2739</v>
       </c>
       <c r="H115" t="n">
-        <v>358.1672</v>
+        <v>351.8625</v>
       </c>
     </row>
     <row r="116">
@@ -4113,29 +4113,29 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9784</v>
+        <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0259</v>
+        <v>0.6365</v>
       </c>
       <c r="G116" t="n">
-        <v>361.3724</v>
+        <v>0.2858</v>
       </c>
       <c r="H116" t="n">
-        <v>639.1536</v>
+        <v>390.426</v>
       </c>
     </row>
     <row r="117">
@@ -4145,29 +4145,29 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9758</v>
+        <v>0.9999</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.0159</v>
+        <v>0.6472</v>
       </c>
       <c r="G117" t="n">
-        <v>366.3521</v>
+        <v>11.6211</v>
       </c>
       <c r="H117" t="n">
-        <v>652.7251</v>
+        <v>384.6211</v>
       </c>
     </row>
     <row r="118">
@@ -4177,29 +4177,29 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.7063</v>
+        <v>0.7207</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0036</v>
+        <v>0.458</v>
       </c>
       <c r="H118" t="n">
-        <v>350.9487</v>
+        <v>342.2374</v>
       </c>
     </row>
     <row r="119">
@@ -4209,29 +4209,29 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0.6472</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>11.6211</v>
+        <v>0.0005</v>
       </c>
       <c r="H119" t="n">
-        <v>384.6211</v>
+        <v>358.1672</v>
       </c>
     </row>
     <row r="120">
@@ -4241,29 +4241,29 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9979</v>
+        <v>0.9784</v>
       </c>
       <c r="F120" t="n">
-        <v>0.5556</v>
+        <v>0.0259</v>
       </c>
       <c r="G120" t="n">
-        <v>52.8341</v>
+        <v>361.3724</v>
       </c>
       <c r="H120" t="n">
-        <v>431.6962</v>
+        <v>639.1536</v>
       </c>
     </row>
     <row r="121">
@@ -4273,29 +4273,29 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9979</v>
+        <v>0.9758</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5556</v>
+        <v>-0.0159</v>
       </c>
       <c r="G121" t="n">
-        <v>52.8341</v>
+        <v>366.3521</v>
       </c>
       <c r="H121" t="n">
-        <v>431.6962</v>
+        <v>652.7251</v>
       </c>
     </row>
     <row r="122">
@@ -4305,29 +4305,29 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.728</v>
+        <v>0.7063</v>
       </c>
       <c r="G122" t="n">
-        <v>18.4072</v>
+        <v>0.0036</v>
       </c>
       <c r="H122" t="n">
-        <v>337.7456</v>
+        <v>350.9487</v>
       </c>
     </row>
     <row r="123">
@@ -4337,11 +4337,11 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4353,13 +4353,13 @@
         <v>0.9999</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6474</v>
+        <v>0.6472</v>
       </c>
       <c r="G123" t="n">
-        <v>11.6246</v>
+        <v>11.6211</v>
       </c>
       <c r="H123" t="n">
-        <v>384.5584</v>
+        <v>384.6211</v>
       </c>
     </row>
     <row r="124">
@@ -4369,29 +4369,29 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="F124" t="n">
-        <v>0.6884</v>
+        <v>0.5556</v>
       </c>
       <c r="G124" t="n">
-        <v>4.0215</v>
+        <v>52.8341</v>
       </c>
       <c r="H124" t="n">
-        <v>361.48</v>
+        <v>431.6962</v>
       </c>
     </row>
     <row r="125">
@@ -4401,29 +4401,29 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>0.9979</v>
       </c>
       <c r="F125" t="n">
-        <v>0.6855</v>
+        <v>0.5556</v>
       </c>
       <c r="G125" t="n">
-        <v>1.7369</v>
+        <v>52.8341</v>
       </c>
       <c r="H125" t="n">
-        <v>363.1774</v>
+        <v>431.6962</v>
       </c>
     </row>
     <row r="126">
@@ -4433,11 +4433,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4446,16 +4446,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9999</v>
+        <v>0.9996</v>
       </c>
       <c r="F126" t="n">
-        <v>0.6192</v>
+        <v>0.728</v>
       </c>
       <c r="G126" t="n">
-        <v>11.2507</v>
+        <v>18.4072</v>
       </c>
       <c r="H126" t="n">
-        <v>399.6025</v>
+        <v>337.7456</v>
       </c>
     </row>
     <row r="127">
@@ -4465,28 +4465,156 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>126</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.6474</v>
+      </c>
+      <c r="G127" t="n">
+        <v>11.6246</v>
+      </c>
+      <c r="H127" t="n">
+        <v>384.5584</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4.0215</v>
+      </c>
+      <c r="H128" t="n">
+        <v>361.48</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>172</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6843</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1.8048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>363.8666</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>173</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.6192</v>
+      </c>
+      <c r="G130" t="n">
+        <v>11.2507</v>
+      </c>
+      <c r="H130" t="n">
+        <v>399.6025</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>total.trans.carotene.natif</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
         <v>174</v>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
-      <c r="E127" t="n">
+      <c r="E131" t="n">
         <v>1</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F131" t="n">
         <v>0.7333</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G131" t="n">
         <v>2.1168</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H131" t="n">
         <v>334.4414</v>
       </c>
     </row>
